--- a/Vf/TABLE_4_5/Table_5_PanelA_Multiplicative_MIDAS.xlsx
+++ b/Vf/TABLE_4_5/Table_5_PanelA_Multiplicative_MIDAS.xlsx
@@ -447,16 +447,16 @@
         <v>-0.9</v>
       </c>
       <c r="B2" t="n">
-        <v>1.072539870792834</v>
+        <v>1.071217143695119</v>
       </c>
       <c r="C2" t="n">
-        <v>1.086862917053146</v>
+        <v>1.08378682312842</v>
       </c>
       <c r="D2" t="n">
-        <v>1.055411358781403</v>
+        <v>1.052890228516783</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9141631866575578</v>
+        <v>0.912901700739755</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>-0.5</v>
       </c>
       <c r="B3" t="n">
-        <v>1.061280562137675</v>
+        <v>1.060462123654305</v>
       </c>
       <c r="C3" t="n">
-        <v>1.150398809583779</v>
+        <v>1.148813940160107</v>
       </c>
       <c r="D3" t="n">
-        <v>1.137780469691637</v>
+        <v>1.136814032762119</v>
       </c>
       <c r="E3" t="n">
-        <v>1.021705776737789</v>
+        <v>1.021408396440925</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1.066307115192855</v>
+        <v>1.066411932200731</v>
       </c>
       <c r="C4" t="n">
-        <v>1.148976373689262</v>
+        <v>1.147413192524126</v>
       </c>
       <c r="D4" t="n">
-        <v>1.128473264335124</v>
+        <v>1.125036310030237</v>
       </c>
       <c r="E4" t="n">
-        <v>1.03900982772799</v>
+        <v>1.038359923290781</v>
       </c>
     </row>
     <row r="5">
@@ -501,13 +501,13 @@
         <v>1.042781640994229</v>
       </c>
       <c r="C5" t="n">
-        <v>1.13605822793437</v>
+        <v>1.133621286920247</v>
       </c>
       <c r="D5" t="n">
-        <v>1.125091959842475</v>
+        <v>1.123186195150528</v>
       </c>
       <c r="E5" t="n">
-        <v>1.041725303307056</v>
+        <v>1.041072365310717</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>0.95</v>
       </c>
       <c r="B6" t="n">
-        <v>0.952792009624518</v>
+        <v>0.9245452218414361</v>
       </c>
       <c r="C6" t="n">
-        <v>1.036255221738639</v>
+        <v>1.033589647456808</v>
       </c>
       <c r="D6" t="n">
-        <v>1.067643879041825</v>
+        <v>1.065969339816734</v>
       </c>
       <c r="E6" t="n">
-        <v>1.066989330028927</v>
+        <v>1.065393709268203</v>
       </c>
     </row>
   </sheetData>
